--- a/data/2026/Liquor 2026/cleaned/liq_sale_jan_26_cleaned.xlsx
+++ b/data/2026/Liquor 2026/cleaned/liq_sale_jan_26_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,2772 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>076001D</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>76001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WHISKY 100 PIPER 750 ML</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>742.62</v>
+      </c>
+      <c r="G2" t="n">
+        <v>816.88</v>
+      </c>
+      <c r="H2" t="n">
+        <v>107</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87406.16</v>
+      </c>
+      <c r="L2" t="n">
+        <v>79460.34</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7945.82</v>
+      </c>
+      <c r="N2" t="n">
+        <v>119</v>
+      </c>
+      <c r="O2" t="n">
+        <v>36</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1748.38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>076003P</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>76003</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S/W BALLENTINES</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>992.25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1091.48</v>
+      </c>
+      <c r="H3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15280.72</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13891.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1389.22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>305.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>076007S</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>76007</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WHISKY VAT 69 FINEST 750 ML</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>694.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>763.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9925.370000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9023.040000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>902.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" t="n">
+        <v>198.51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>076010X</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WHISKY TEACHER HIGHLAND 750ML</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>719.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>791.8200000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>53</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>53</v>
+      </c>
+      <c r="K5" t="n">
+        <v>41966.46</v>
+      </c>
+      <c r="L5" t="n">
+        <v>38151.52</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3814.94</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="n">
+        <v>31</v>
+      </c>
+      <c r="P5" t="n">
+        <v>839.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>076018A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>76018</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SCOTCH WKY B/DOG TRIPLE</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1038.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1142.17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31</v>
+      </c>
+      <c r="K6" t="n">
+        <v>35407.27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32188.54</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3218.73</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" t="n">
+        <v>708.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>076021B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>76021</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WHISKY BLACK DOG CENTEARY BLACK 750</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>742.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>816.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>600</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>61</v>
+      </c>
+      <c r="K7" t="n">
+        <v>49814.43</v>
+      </c>
+      <c r="L7" t="n">
+        <v>45285.79</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4528.64</v>
+      </c>
+      <c r="N7" t="n">
+        <v>61</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>996.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>076038H</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>76038</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S/W BLACK &amp;  WHITE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>735.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>808.9400000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36</v>
+      </c>
+      <c r="K8" t="n">
+        <v>29121.84</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26474.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2647.44</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>582.48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>076041A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>76041</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100 PIPIER 12 YEARS 750 ML</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1005.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1106.51</v>
+      </c>
+      <c r="H9" t="n">
+        <v>123</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34</v>
+      </c>
+      <c r="K9" t="n">
+        <v>37621.34</v>
+      </c>
+      <c r="L9" t="n">
+        <v>34201.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3420.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" t="n">
+        <v>752.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>076042L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>76042</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S/WHY RAMPOOR INDIAN SINGLE MALT</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>4199.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4619.82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>46198.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>41998.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4199.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>076043P</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>76043</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PAUL JOHN IND SINGLE MALT WHY</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1574.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1731.64</v>
+      </c>
+      <c r="H11" t="n">
+        <v>145</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5194.92</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4722.66</v>
+      </c>
+      <c r="M11" t="n">
+        <v>472.26</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>103.89</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>076045A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>76045</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INDRI MALT WHISKY</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2110.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2322.05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K12" t="n">
+        <v>46441</v>
+      </c>
+      <c r="L12" t="n">
+        <v>42219</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4222</v>
+      </c>
+      <c r="N12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17</v>
+      </c>
+      <c r="P12" t="n">
+        <v>928.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>078151Y</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>78151</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RUM BLACK BULL 5 YEAR OLD</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="H13" t="n">
+        <v>75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8658.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7871.25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>60</v>
+      </c>
+      <c r="O13" t="n">
+        <v>105</v>
+      </c>
+      <c r="P13" t="n">
+        <v>173.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>078152S</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>78152</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RUM CONTESSA 5 YEAR OLD</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>112.33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>123.56</v>
+      </c>
+      <c r="H14" t="n">
+        <v>192</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>192</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23723.52</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21567.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2156.16</v>
+      </c>
+      <c r="N14" t="n">
+        <v>162</v>
+      </c>
+      <c r="O14" t="n">
+        <v>150</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>078154K</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>78154</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RUM OLD MONK 7 YEARS OLD</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>117.88</v>
+      </c>
+      <c r="G15" t="n">
+        <v>129.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>345</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>345</v>
+      </c>
+      <c r="K15" t="n">
+        <v>44736.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40668.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4067.55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>301</v>
+      </c>
+      <c r="O15" t="n">
+        <v>280</v>
+      </c>
+      <c r="P15" t="n">
+        <v>893.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>078155X</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>78155</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RUM OLD SMUGLER XXX 750ML</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>132.44</v>
+      </c>
+      <c r="H16" t="n">
+        <v>245</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>245</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32447.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>29498</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2949.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>245</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>649.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>078195A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>78195</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RUM MADIRA</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>112.69</v>
+      </c>
+      <c r="G17" t="n">
+        <v>123.96</v>
+      </c>
+      <c r="H17" t="n">
+        <v>121</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>121</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14999.16</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13635.49</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1363.67</v>
+      </c>
+      <c r="N17" t="n">
+        <v>92</v>
+      </c>
+      <c r="O17" t="n">
+        <v>211</v>
+      </c>
+      <c r="P17" t="n">
+        <v>300.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>078198A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>78198</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RUM BACARDI LIMON</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>223.68</v>
+      </c>
+      <c r="G18" t="n">
+        <v>246.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23374.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21249.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2125.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>80</v>
+      </c>
+      <c r="O18" t="n">
+        <v>225</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>078202A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>78202</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>XXX SUNNY RUM 750 ML</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>109.46</v>
+      </c>
+      <c r="G19" t="n">
+        <v>120.41</v>
+      </c>
+      <c r="H19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3130.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2845.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>284.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>24</v>
+      </c>
+      <c r="O19" t="n">
+        <v>58</v>
+      </c>
+      <c r="P19" t="n">
+        <v>62.66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>078203P</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>78203</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RUM GENIOUS</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>114.98</v>
+      </c>
+      <c r="G20" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3035.52</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2759.52</v>
+      </c>
+      <c r="M20" t="n">
+        <v>276</v>
+      </c>
+      <c r="N20" t="n">
+        <v>24</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>60.72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>078207R</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>78207</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RUM 1965 SPRIT OF VICTORY PREM 750</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>133.93</v>
+      </c>
+      <c r="G21" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>308</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>308</v>
+      </c>
+      <c r="K21" t="n">
+        <v>45374.56</v>
+      </c>
+      <c r="L21" t="n">
+        <v>41250.44</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4124.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>281</v>
+      </c>
+      <c r="O21" t="n">
+        <v>393</v>
+      </c>
+      <c r="P21" t="n">
+        <v>908.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>078208T</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>78208</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RUM COMMANDER IN CHIEF 750ML</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>143.15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>240</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>240</v>
+      </c>
+      <c r="K22" t="n">
+        <v>34356</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31233.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3122.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>240</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>686.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>078209P</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>78209</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BACARDI CLSSIC BLACK ORIGINAAL</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>146.32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>160.95</v>
+      </c>
+      <c r="H23" t="n">
+        <v>79</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>79</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12715.05</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11559.28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1155.77</v>
+      </c>
+      <c r="N23" t="n">
+        <v>60</v>
+      </c>
+      <c r="O23" t="n">
+        <v>257</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>078211L</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>78211</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LION DADDY ORIGINAL RUM</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>136.27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>96</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>14390.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13081.92</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1308.48</v>
+      </c>
+      <c r="N24" t="n">
+        <v>96</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>079006B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>79006</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BEER KING FISHER STRONG PREMIUM</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="G25" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="H25" t="n">
+        <v>97</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>97</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7961.76</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7582.49</v>
+      </c>
+      <c r="M25" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>144</v>
+      </c>
+      <c r="O25" t="n">
+        <v>335</v>
+      </c>
+      <c r="P25" t="n">
+        <v>159.08</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>079032L</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>79032</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BDWISER CAN BEER STRONG</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="G26" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>306</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>306</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20804.94</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19813.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>991.4400000000001</v>
+      </c>
+      <c r="N26" t="n">
+        <v>192</v>
+      </c>
+      <c r="O26" t="n">
+        <v>486</v>
+      </c>
+      <c r="P26" t="n">
+        <v>416.16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>079054S</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>79054</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BRANDY MORPHEUS XO BLINDED PREM</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>406.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>446.93</v>
+      </c>
+      <c r="H27" t="n">
+        <v>52</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>52</v>
+      </c>
+      <c r="K27" t="n">
+        <v>23240.36</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21127.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2112.76</v>
+      </c>
+      <c r="N27" t="n">
+        <v>49</v>
+      </c>
+      <c r="O27" t="n">
+        <v>57</v>
+      </c>
+      <c r="P27" t="n">
+        <v>464.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>079081L</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>79081</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BRANDY MANSION</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>318.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>349.86</v>
+      </c>
+      <c r="H28" t="n">
+        <v>52</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>52</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18192.72</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16538.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1654.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>51</v>
+      </c>
+      <c r="O28" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>079105K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>79105</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JAISALMIR INDIA CEAFT GIN</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1904.46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2094.91</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6284.73</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5713.38</v>
+      </c>
+      <c r="M29" t="n">
+        <v>571.35</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>125.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>079106H</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>79106</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GIN  GREATER THAN LONDON</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>454.15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>499.57</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3496.99</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3179.05</v>
+      </c>
+      <c r="M30" t="n">
+        <v>317.94</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>69.93000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>079152L</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>79152</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VODKA M/M GREEN APPLEV</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>281.32</v>
+      </c>
+      <c r="G31" t="n">
+        <v>309.45</v>
+      </c>
+      <c r="H31" t="n">
+        <v>36</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>36</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11140.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10127.52</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1012.68</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36</v>
+      </c>
+      <c r="O31" t="n">
+        <v>36</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>079153V</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>79153</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VODKA ORANGE MAGIC MOMENT 750 ML</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>281.32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>309.45</v>
+      </c>
+      <c r="H32" t="n">
+        <v>37</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>37</v>
+      </c>
+      <c r="K32" t="n">
+        <v>11449.65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10408.84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1040.81</v>
+      </c>
+      <c r="N32" t="n">
+        <v>36</v>
+      </c>
+      <c r="O32" t="n">
+        <v>35</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>079156X</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>79156</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VODKA SMIRNOFF 750 ML</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="G33" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>21</v>
+      </c>
+      <c r="K33" t="n">
+        <v>8284.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7531.44</v>
+      </c>
+      <c r="M33" t="n">
+        <v>753.0599999999999</v>
+      </c>
+      <c r="N33" t="n">
+        <v>24</v>
+      </c>
+      <c r="O33" t="n">
+        <v>15</v>
+      </c>
+      <c r="P33" t="n">
+        <v>165.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>079162D</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>79162</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VODKA MAGIC MOVEMENT</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>289.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v>318.99</v>
+      </c>
+      <c r="H34" t="n">
+        <v>37</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>37</v>
+      </c>
+      <c r="K34" t="n">
+        <v>11802.63</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10729.63</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1073</v>
+      </c>
+      <c r="N34" t="n">
+        <v>36</v>
+      </c>
+      <c r="O34" t="n">
+        <v>35</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>079198T</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>79198</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WHISKY MC.DOWEL NO.1 750 ML.</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>291.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>168</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>168</v>
+      </c>
+      <c r="K35" t="n">
+        <v>49027.44</v>
+      </c>
+      <c r="L35" t="n">
+        <v>44570.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4457.04</v>
+      </c>
+      <c r="N35" t="n">
+        <v>121</v>
+      </c>
+      <c r="O35" t="n">
+        <v>73</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>079230S</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>79230</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WHISKY BLENDER PRIDE R/PRIMIUM</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>436.33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>479.96</v>
+      </c>
+      <c r="H36" t="n">
+        <v>228</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>228</v>
+      </c>
+      <c r="K36" t="n">
+        <v>109430.88</v>
+      </c>
+      <c r="L36" t="n">
+        <v>99483.24000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9947.639999999999</v>
+      </c>
+      <c r="N36" t="n">
+        <v>182</v>
+      </c>
+      <c r="O36" t="n">
+        <v>182</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2188.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>079232K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>79232</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WHISKY ROYAL STAG BLENDED</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>293.95</v>
+      </c>
+      <c r="G37" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>299</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>299</v>
+      </c>
+      <c r="K37" t="n">
+        <v>96681.64999999999</v>
+      </c>
+      <c r="L37" t="n">
+        <v>87891.05</v>
+      </c>
+      <c r="M37" t="n">
+        <v>8790.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>216</v>
+      </c>
+      <c r="O37" t="n">
+        <v>169</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1934.53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>079243J</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>79243</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WHY AFTER DARK GRAIN</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>405.24</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" t="n">
+        <v>9725.76</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8841.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>884.16</v>
+      </c>
+      <c r="N38" t="n">
+        <v>24</v>
+      </c>
+      <c r="O38" t="n">
+        <v>60</v>
+      </c>
+      <c r="P38" t="n">
+        <v>194.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>079266A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>79266</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FRATELLI WINES SETTLE 750 ML</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1195.58</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1315.14</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3945.42</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3586.74</v>
+      </c>
+      <c r="M39" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12</v>
+      </c>
+      <c r="O39" t="n">
+        <v>9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>079276K</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>79276</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>B BACARDI CRANE</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="G40" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="H40" t="n">
+        <v>27</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>27</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1201.23</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1143.99</v>
+      </c>
+      <c r="M40" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="N40" t="n">
+        <v>48</v>
+      </c>
+      <c r="O40" t="n">
+        <v>69</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>079283G</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>79283</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WINE CLASSIC SHIRAZ 750ML</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="G41" t="n">
+        <v>349.22</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2095.32</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1904.82</v>
+      </c>
+      <c r="M41" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>41.88</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>079312W</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>79312</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>WHISKY WHITE&amp; BLUE PREMIUM</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>300.45</v>
+      </c>
+      <c r="G42" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>113</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>113</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37346.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33950.85</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3395.65</v>
+      </c>
+      <c r="N42" t="n">
+        <v>108</v>
+      </c>
+      <c r="O42" t="n">
+        <v>55</v>
+      </c>
+      <c r="P42" t="n">
+        <v>746.9299999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>079313P</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>79313</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AMRUT AMALGAM MALT WHISKY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1317.11</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1448.82</v>
+      </c>
+      <c r="H43" t="n">
+        <v>17</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" t="n">
+        <v>24629.94</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22390.87</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2239.07</v>
+      </c>
+      <c r="N43" t="n">
+        <v>50</v>
+      </c>
+      <c r="O43" t="n">
+        <v>33</v>
+      </c>
+      <c r="P43" t="n">
+        <v>492.66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>079317P</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>79317</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WHY ROCK FORD</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>494.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>543.62</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>24</v>
+      </c>
+      <c r="K44" t="n">
+        <v>13046.88</v>
+      </c>
+      <c r="L44" t="n">
+        <v>11860.8</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1186.08</v>
+      </c>
+      <c r="N44" t="n">
+        <v>24</v>
+      </c>
+      <c r="O44" t="n">
+        <v>24</v>
+      </c>
+      <c r="P44" t="n">
+        <v>260.88</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>079318A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>79318</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>STERLING RESRVE B10 WHY</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>439.27</v>
+      </c>
+      <c r="G45" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>24</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>24</v>
+      </c>
+      <c r="K45" t="n">
+        <v>11596.8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10542.48</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1054.32</v>
+      </c>
+      <c r="N45" t="n">
+        <v>24</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>231.84</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>079322A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>79322</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WHISKY BLEDERS PRAIDE R</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>508.76</v>
+      </c>
+      <c r="G46" t="n">
+        <v>559.64</v>
+      </c>
+      <c r="H46" t="n">
+        <v>48</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>48</v>
+      </c>
+      <c r="K46" t="n">
+        <v>26862.72</v>
+      </c>
+      <c r="L46" t="n">
+        <v>24420.48</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2442.24</v>
+      </c>
+      <c r="N46" t="n">
+        <v>48</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>537.12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>079324E</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>79324</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WHY DENNIS 750ML</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>263.56</v>
+      </c>
+      <c r="H47" t="n">
+        <v>178</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>178</v>
+      </c>
+      <c r="K47" t="n">
+        <v>46913.68</v>
+      </c>
+      <c r="L47" t="n">
+        <v>42648.8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4264.88</v>
+      </c>
+      <c r="N47" t="n">
+        <v>168</v>
+      </c>
+      <c r="O47" t="n">
+        <v>134</v>
+      </c>
+      <c r="P47" t="n">
+        <v>938.0599999999999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>079329F</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>79329</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OAKEN GLOW WHISKY</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>415.19</v>
+      </c>
+      <c r="G48" t="n">
+        <v>456.71</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5480.52</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4982.28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>498.24</v>
+      </c>
+      <c r="N48" t="n">
+        <v>12</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>109.56</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Group Total</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>4047</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4047</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1225963.25</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1115807.94</v>
+      </c>
+      <c r="M49" t="n">
+        <v>110155.31</v>
+      </c>
+      <c r="N49" t="n">
+        <v>21631.3</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/2026/Liquor 2026/cleaned/liq_sale_jan_26_cleaned.xlsx
+++ b/data/2026/Liquor 2026/cleaned/liq_sale_jan_26_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,51 +521,51 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>076001D</t>
+          <t>079275A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WHISKY 100 PIPER 750 ML</t>
+          <t>SULA RED WINE 750 ML</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>742.62</v>
+        <v>362.73</v>
       </c>
       <c r="G2" t="n">
-        <v>816.88</v>
+        <v>399</v>
       </c>
       <c r="H2" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>87406.16</v>
+        <v>3990</v>
       </c>
       <c r="L2" t="n">
-        <v>79460.34</v>
+        <v>3627.3</v>
       </c>
       <c r="M2" t="n">
-        <v>7945.82</v>
+        <v>362.7</v>
       </c>
       <c r="N2" t="n">
-        <v>119</v>
+        <v>271</v>
       </c>
       <c r="O2" t="n">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="P2" t="n">
-        <v>1748.38</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="3">
@@ -579,51 +579,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>076003P</t>
+          <t>079081L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>76003</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S/W BALLENTINES</t>
+          <t>BRANDY MANSION</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>992.25</v>
+        <v>318.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1091.48</v>
+        <v>349.86</v>
       </c>
       <c r="H3" t="n">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>15280.72</v>
+        <v>5597.76</v>
       </c>
       <c r="L3" t="n">
-        <v>13891.5</v>
+        <v>5088.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1389.22</v>
+        <v>508.96</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="O3" t="n">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
-        <v>305.62</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="4">
@@ -657,31 +657,31 @@
         <v>763.49</v>
       </c>
       <c r="H4" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="K4" t="n">
-        <v>9925.370000000001</v>
+        <v>62606.18</v>
       </c>
       <c r="L4" t="n">
-        <v>9023.040000000001</v>
+        <v>56914.56</v>
       </c>
       <c r="M4" t="n">
-        <v>902.33</v>
+        <v>5691.62</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>294</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="P4" t="n">
-        <v>198.51</v>
+        <v>1101.27</v>
       </c>
     </row>
     <row r="5">
@@ -695,51 +695,51 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>076010X</t>
+          <t>076038H</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>76038</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WHISKY TEACHER HIGHLAND 750ML</t>
+          <t>S/W BLACK &amp;  WHITE</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>719.84</v>
+        <v>735.4</v>
       </c>
       <c r="G5" t="n">
-        <v>791.8200000000001</v>
+        <v>808.9400000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K5" t="n">
-        <v>41966.46</v>
+        <v>44491.7</v>
       </c>
       <c r="L5" t="n">
-        <v>38151.52</v>
+        <v>40447</v>
       </c>
       <c r="M5" t="n">
-        <v>3814.94</v>
+        <v>4044.7</v>
       </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>839.52</v>
+        <v>782.63</v>
       </c>
     </row>
     <row r="6">
@@ -753,51 +753,51 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>076018A</t>
+          <t>079198T</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>79198</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SCOTCH WKY B/DOG TRIPLE</t>
+          <t>WHISKY MC.DOWEL NO.1 750 ML.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1038.34</v>
+        <v>265.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1142.17</v>
+        <v>291.83</v>
       </c>
       <c r="H6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
-        <v>35407.27</v>
+        <v>11965.03</v>
       </c>
       <c r="L6" t="n">
-        <v>32188.54</v>
+        <v>10877.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3218.73</v>
+        <v>1087.73</v>
       </c>
       <c r="N6" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="P6" t="n">
-        <v>708.04</v>
+        <v>210.47</v>
       </c>
     </row>
     <row r="7">
@@ -811,51 +811,51 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>076021B</t>
+          <t>079322A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>79322</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WHISKY BLACK DOG CENTEARY BLACK 750</t>
+          <t>WHISKY BLEDERS PRAIDE R</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>742.39</v>
+        <v>508.76</v>
       </c>
       <c r="G7" t="n">
-        <v>816.63</v>
+        <v>559.64</v>
       </c>
       <c r="H7" t="n">
-        <v>600</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>49814.43</v>
+        <v>4477.12</v>
       </c>
       <c r="L7" t="n">
-        <v>45285.79</v>
+        <v>4070.08</v>
       </c>
       <c r="M7" t="n">
-        <v>4528.64</v>
+        <v>407.04</v>
       </c>
       <c r="N7" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="O7" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="P7" t="n">
-        <v>996.13</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="8">
@@ -869,51 +869,51 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>076038H</t>
+          <t>076043P</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>76038</t>
+          <t>76043</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S/W BLACK &amp;  WHITE</t>
+          <t>PAUL JOHN IND SINGLE MALT WHY</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>735.4</v>
+        <v>1574.22</v>
       </c>
       <c r="G8" t="n">
-        <v>808.9400000000001</v>
+        <v>1731.64</v>
       </c>
       <c r="H8" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>29121.84</v>
+        <v>15584.76</v>
       </c>
       <c r="L8" t="n">
-        <v>26474.4</v>
+        <v>14167.98</v>
       </c>
       <c r="M8" t="n">
-        <v>2647.44</v>
+        <v>1416.78</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="O8" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="P8" t="n">
-        <v>582.48</v>
+        <v>274.14</v>
       </c>
     </row>
     <row r="9">
@@ -927,51 +927,51 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>076041A</t>
+          <t>079153V</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>76041</t>
+          <t>79153</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100 PIPIER 12 YEARS 750 ML</t>
+          <t>VODKA ORANGE MAGIC MOMENT 750 ML</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1005.92</v>
+        <v>281.32</v>
       </c>
       <c r="G9" t="n">
-        <v>1106.51</v>
+        <v>309.45</v>
       </c>
       <c r="H9" t="n">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" t="n">
-        <v>37621.34</v>
+        <v>11759.1</v>
       </c>
       <c r="L9" t="n">
-        <v>34201.28</v>
+        <v>10690.16</v>
       </c>
       <c r="M9" t="n">
-        <v>3420.06</v>
+        <v>1068.94</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
-        <v>752.42</v>
+        <v>206.85</v>
       </c>
     </row>
     <row r="10">
@@ -985,51 +985,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>076042L</t>
+          <t>079006B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76042</t>
+          <t>79006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S/WHY RAMPOOR INDIAN SINGLE MALT</t>
+          <t>BEER KING FISHER STRONG PREMIUM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4199.84</v>
+        <v>78.17</v>
       </c>
       <c r="G10" t="n">
-        <v>4619.82</v>
+        <v>82.08</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>46198.2</v>
+        <v>1067.04</v>
       </c>
       <c r="L10" t="n">
-        <v>41998.4</v>
+        <v>1016.21</v>
       </c>
       <c r="M10" t="n">
-        <v>4199.8</v>
+        <v>50.83</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="P10" t="n">
-        <v>924</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="11">
@@ -1043,51 +1043,51 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>076043P</t>
+          <t>078198A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>76043</t>
+          <t>78198</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PAUL JOHN IND SINGLE MALT WHY</t>
+          <t>RUM BACARDI LIMON</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1574.22</v>
+        <v>223.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1731.64</v>
+        <v>246.05</v>
       </c>
       <c r="H11" t="n">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>5194.92</v>
+        <v>7873.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4722.66</v>
+        <v>7157.76</v>
       </c>
       <c r="M11" t="n">
-        <v>472.26</v>
+        <v>715.84</v>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
-        <v>103.89</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="12">
@@ -1101,51 +1101,51 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>076045A</t>
+          <t>078207R</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>76045</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INDRI MALT WHISKY</t>
+          <t>RUM 1965 SPRIT OF VICTORY PREM 750</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2110.95</v>
+        <v>133.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2322.05</v>
+        <v>147.32</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="K12" t="n">
-        <v>46441</v>
+        <v>11932.92</v>
       </c>
       <c r="L12" t="n">
-        <v>42219</v>
+        <v>10848.33</v>
       </c>
       <c r="M12" t="n">
-        <v>4222</v>
+        <v>1084.59</v>
       </c>
       <c r="N12" t="n">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="P12" t="n">
-        <v>928.8</v>
+        <v>209.91</v>
       </c>
     </row>
     <row r="13">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>078151Y</t>
+          <t>079156X</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>78151</t>
+          <t>79156</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RUM BLACK BULL 5 YEAR OLD</t>
+          <t>VODKA SMIRNOFF 750 ML</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>104.95</v>
+        <v>358.64</v>
       </c>
       <c r="G13" t="n">
-        <v>115.45</v>
+        <v>394.5</v>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>8658.75</v>
+        <v>11046</v>
       </c>
       <c r="L13" t="n">
-        <v>7871.25</v>
+        <v>10041.92</v>
       </c>
       <c r="M13" t="n">
-        <v>787.5</v>
+        <v>1004.08</v>
       </c>
       <c r="N13" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="O13" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="P13" t="n">
-        <v>173.25</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="14">
@@ -1217,51 +1217,51 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>078152S</t>
+          <t>078203P</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>78152</t>
+          <t>78203</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RUM CONTESSA 5 YEAR OLD</t>
+          <t>RUM GENIOUS</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>112.33</v>
+        <v>114.98</v>
       </c>
       <c r="G14" t="n">
-        <v>123.56</v>
+        <v>126.48</v>
       </c>
       <c r="H14" t="n">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>23723.52</v>
+        <v>2782.56</v>
       </c>
       <c r="L14" t="n">
-        <v>21567.36</v>
+        <v>2529.56</v>
       </c>
       <c r="M14" t="n">
-        <v>2156.16</v>
+        <v>253</v>
       </c>
       <c r="N14" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="O14" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="15">
@@ -1275,51 +1275,51 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>078154K</t>
+          <t>079329F</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>78154</t>
+          <t>79329</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RUM OLD MONK 7 YEARS OLD</t>
+          <t>OAKEN GLOW WHISKY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>117.88</v>
+        <v>415.19</v>
       </c>
       <c r="G15" t="n">
-        <v>129.67</v>
+        <v>456.71</v>
       </c>
       <c r="H15" t="n">
-        <v>345</v>
+        <v>69</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>345</v>
+        <v>67</v>
       </c>
       <c r="K15" t="n">
-        <v>44736.15</v>
+        <v>30599.57</v>
       </c>
       <c r="L15" t="n">
-        <v>40668.6</v>
+        <v>27817.73</v>
       </c>
       <c r="M15" t="n">
-        <v>4067.55</v>
+        <v>2781.84</v>
       </c>
       <c r="N15" t="n">
-        <v>301</v>
+        <v>59</v>
       </c>
       <c r="O15" t="n">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="P15" t="n">
-        <v>893.55</v>
+        <v>538.26</v>
       </c>
     </row>
     <row r="16">
@@ -1333,51 +1333,51 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>078155X</t>
+          <t>076041A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>78155</t>
+          <t>76041</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RUM OLD SMUGLER XXX 750ML</t>
+          <t>100 PIPIER 12 YEARS 750 ML</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>120.4</v>
+        <v>1005.92</v>
       </c>
       <c r="G16" t="n">
-        <v>132.44</v>
+        <v>1106.51</v>
       </c>
       <c r="H16" t="n">
-        <v>245</v>
+        <v>54</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>245</v>
+        <v>54</v>
       </c>
       <c r="K16" t="n">
-        <v>32447.8</v>
+        <v>59751.54</v>
       </c>
       <c r="L16" t="n">
-        <v>29498</v>
+        <v>54319.68</v>
       </c>
       <c r="M16" t="n">
-        <v>2949.8</v>
+        <v>5431.86</v>
       </c>
       <c r="N16" t="n">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="P16" t="n">
-        <v>649.25</v>
+        <v>1051.06</v>
       </c>
     </row>
     <row r="17">
@@ -1391,51 +1391,51 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078195A</t>
+          <t>079232K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>78195</t>
+          <t>79232</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RUM MADIRA</t>
+          <t>WHISKY ROYAL STAG BLENDED</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>112.69</v>
+        <v>293.95</v>
       </c>
       <c r="G17" t="n">
-        <v>123.96</v>
+        <v>323.35</v>
       </c>
       <c r="H17" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="K17" t="n">
-        <v>14999.16</v>
+        <v>21987.8</v>
       </c>
       <c r="L17" t="n">
-        <v>13635.49</v>
+        <v>19988.6</v>
       </c>
       <c r="M17" t="n">
-        <v>1363.67</v>
+        <v>1999.2</v>
       </c>
       <c r="N17" t="n">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="O17" t="n">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="P17" t="n">
-        <v>300.08</v>
+        <v>386.77</v>
       </c>
     </row>
     <row r="18">
@@ -1449,51 +1449,51 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>078198A</t>
+          <t>079032L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78198</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RUM BACARDI LIMON</t>
+          <t>BDWISER CAN BEER STRONG</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>223.68</v>
+        <v>64.75</v>
       </c>
       <c r="G18" t="n">
-        <v>246.05</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="K18" t="n">
-        <v>23374.75</v>
+        <v>3603.47</v>
       </c>
       <c r="L18" t="n">
-        <v>21249.6</v>
+        <v>3431.75</v>
       </c>
       <c r="M18" t="n">
-        <v>2125.15</v>
+        <v>171.72</v>
       </c>
       <c r="N18" t="n">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="O18" t="n">
-        <v>225</v>
+        <v>116</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1507,51 +1507,51 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>078202A</t>
+          <t>079317P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>78202</t>
+          <t>79317</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>XXX SUNNY RUM 750 ML</t>
+          <t>WHY ROCK FORD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>109.46</v>
+        <v>494.2</v>
       </c>
       <c r="G19" t="n">
-        <v>120.41</v>
+        <v>543.62</v>
       </c>
       <c r="H19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>3130.66</v>
+        <v>14677.74</v>
       </c>
       <c r="L19" t="n">
-        <v>2845.96</v>
+        <v>13343.4</v>
       </c>
       <c r="M19" t="n">
-        <v>284.7</v>
+        <v>1334.34</v>
       </c>
       <c r="N19" t="n">
-        <v>24</v>
+        <v>269</v>
       </c>
       <c r="O19" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P19" t="n">
-        <v>62.66</v>
+        <v>258.19</v>
       </c>
     </row>
     <row r="20">
@@ -1565,51 +1565,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>078203P</t>
+          <t>079152L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>78203</t>
+          <t>79152</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RUM GENIOUS</t>
+          <t>VODKA M/M GREEN APPLEV</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>114.98</v>
+        <v>281.32</v>
       </c>
       <c r="G20" t="n">
-        <v>126.48</v>
+        <v>309.45</v>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>3035.52</v>
+        <v>13925.25</v>
       </c>
       <c r="L20" t="n">
-        <v>2759.52</v>
+        <v>12659.4</v>
       </c>
       <c r="M20" t="n">
-        <v>276</v>
+        <v>1265.85</v>
       </c>
       <c r="N20" t="n">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="P20" t="n">
-        <v>60.72</v>
+        <v>244.95</v>
       </c>
     </row>
     <row r="21">
@@ -1623,51 +1623,51 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>078207R</t>
+          <t>076045A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>76045</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RUM 1965 SPRIT OF VICTORY PREM 750</t>
+          <t>INDRI MALT WHISKY</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>133.93</v>
+        <v>2110.95</v>
       </c>
       <c r="G21" t="n">
-        <v>147.32</v>
+        <v>2322.05</v>
       </c>
       <c r="H21" t="n">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>45374.56</v>
+        <v>48763.05</v>
       </c>
       <c r="L21" t="n">
-        <v>41250.44</v>
+        <v>44329.95</v>
       </c>
       <c r="M21" t="n">
-        <v>4124.12</v>
+        <v>4433.1</v>
       </c>
       <c r="N21" t="n">
-        <v>281</v>
+        <v>36</v>
       </c>
       <c r="O21" t="n">
-        <v>393</v>
+        <v>51</v>
       </c>
       <c r="P21" t="n">
-        <v>908.6</v>
+        <v>857.76</v>
       </c>
     </row>
     <row r="22">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>078208T</t>
+          <t>078211L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>78208</t>
+          <t>78211</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RUM COMMANDER IN CHIEF 750ML</t>
+          <t>LION DADDY ORIGINAL RUM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>130.14</v>
+        <v>136.27</v>
       </c>
       <c r="G22" t="n">
-        <v>143.15</v>
+        <v>149.9</v>
       </c>
       <c r="H22" t="n">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
-        <v>34356</v>
+        <v>3747.5</v>
       </c>
       <c r="L22" t="n">
-        <v>31233.6</v>
+        <v>3406.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3122.4</v>
+        <v>340.75</v>
       </c>
       <c r="N22" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P22" t="n">
-        <v>686.4</v>
+        <v>65.92</v>
       </c>
     </row>
     <row r="23">
@@ -1739,51 +1739,51 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>078209P</t>
+          <t>079230S</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>78209</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BACARDI CLSSIC BLACK ORIGINAAL</t>
+          <t>WHISKY BLENDER PRIDE R/PRIMIUM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>146.32</v>
+        <v>436.33</v>
       </c>
       <c r="G23" t="n">
-        <v>160.95</v>
+        <v>479.96</v>
       </c>
       <c r="H23" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>12715.05</v>
+        <v>11999</v>
       </c>
       <c r="L23" t="n">
-        <v>11559.28</v>
+        <v>10908.25</v>
       </c>
       <c r="M23" t="n">
-        <v>1155.77</v>
+        <v>1090.75</v>
       </c>
       <c r="N23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>257</v>
+        <v>35</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>211.07</v>
       </c>
     </row>
     <row r="24">
@@ -1797,51 +1797,51 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>078211L</t>
+          <t>076021B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>76021</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LION DADDY ORIGINAL RUM</t>
+          <t>WHISKY BLACK DOG CENTEARY BLACK 750</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>136.27</v>
+        <v>742.39</v>
       </c>
       <c r="G24" t="n">
-        <v>149.9</v>
+        <v>816.63</v>
       </c>
       <c r="H24" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>14390.4</v>
+        <v>9799.559999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>13081.92</v>
+        <v>8908.68</v>
       </c>
       <c r="M24" t="n">
-        <v>1308.48</v>
+        <v>890.88</v>
       </c>
       <c r="N24" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="P24" t="n">
-        <v>288</v>
+        <v>172.38</v>
       </c>
     </row>
     <row r="25">
@@ -1855,51 +1855,51 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>079006B</t>
+          <t>079030L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>79006</t>
+          <t>79030</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BEER KING FISHER STRONG PREMIUM</t>
+          <t>BUDWISER CAN BEER PREMIEM</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>78.17</v>
+        <v>56.9</v>
       </c>
       <c r="G25" t="n">
-        <v>82.08</v>
+        <v>59.75</v>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K25" t="n">
-        <v>7961.76</v>
+        <v>5377.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7582.49</v>
+        <v>5121</v>
       </c>
       <c r="M25" t="n">
-        <v>379.27</v>
+        <v>256.5</v>
       </c>
       <c r="N25" t="n">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="O25" t="n">
-        <v>335</v>
+        <v>109</v>
       </c>
       <c r="P25" t="n">
-        <v>159.08</v>
+        <v>99.09</v>
       </c>
     </row>
     <row r="26">
@@ -1913,51 +1913,51 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>079032L</t>
+          <t>076042L</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>79032</t>
+          <t>76042</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BDWISER CAN BEER STRONG</t>
+          <t>S/WHY RAMPOOR INDIAN SINGLE MALT</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>64.75</v>
+        <v>4199.84</v>
       </c>
       <c r="G26" t="n">
-        <v>67.98999999999999</v>
+        <v>4619.82</v>
       </c>
       <c r="H26" t="n">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>20804.94</v>
+        <v>198652.26</v>
       </c>
       <c r="L26" t="n">
-        <v>19813.5</v>
+        <v>180593.12</v>
       </c>
       <c r="M26" t="n">
-        <v>991.4400000000001</v>
+        <v>18059.14</v>
       </c>
       <c r="N26" t="n">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="O26" t="n">
-        <v>486</v>
+        <v>179</v>
       </c>
       <c r="P26" t="n">
-        <v>416.16</v>
+        <v>3494.38</v>
       </c>
     </row>
     <row r="27">
@@ -1971,51 +1971,51 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>079054S</t>
+          <t>079282K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>79054</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BRANDY MORPHEUS XO BLINDED PREM</t>
+          <t>WINE CABERNET SAUVIGNON</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>406.3</v>
+        <v>421.62</v>
       </c>
       <c r="G27" t="n">
-        <v>446.93</v>
+        <v>463.78</v>
       </c>
       <c r="H27" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K27" t="n">
-        <v>23240.36</v>
+        <v>21333.88</v>
       </c>
       <c r="L27" t="n">
-        <v>21127.6</v>
+        <v>19394.52</v>
       </c>
       <c r="M27" t="n">
-        <v>2112.76</v>
+        <v>1939.36</v>
       </c>
       <c r="N27" t="n">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="O27" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="P27" t="n">
-        <v>464.88</v>
+        <v>375.27</v>
       </c>
     </row>
     <row r="28">
@@ -2029,51 +2029,51 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>079081L</t>
+          <t>079162D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>79081</t>
+          <t>79162</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BRANDY MANSION</t>
+          <t>VODKA MAGIC MOVEMENT</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>318.05</v>
+        <v>289.99</v>
       </c>
       <c r="G28" t="n">
-        <v>349.86</v>
+        <v>318.99</v>
       </c>
       <c r="H28" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K28" t="n">
-        <v>18192.72</v>
+        <v>14354.55</v>
       </c>
       <c r="L28" t="n">
-        <v>16538.6</v>
+        <v>13049.55</v>
       </c>
       <c r="M28" t="n">
-        <v>1654.12</v>
+        <v>1305</v>
       </c>
       <c r="N28" t="n">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="O28" t="n">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="P28" t="n">
-        <v>364</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="29">
@@ -2087,51 +2087,51 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>079105K</t>
+          <t>078151Y</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>79105</t>
+          <t>78151</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JAISALMIR INDIA CEAFT GIN</t>
+          <t>RUM BLACK BULL 5 YEAR OLD</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1904.46</v>
+        <v>104.95</v>
       </c>
       <c r="G29" t="n">
-        <v>2094.91</v>
+        <v>115.45</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>6284.73</v>
+        <v>1269.95</v>
       </c>
       <c r="L29" t="n">
-        <v>5713.38</v>
+        <v>1154.45</v>
       </c>
       <c r="M29" t="n">
-        <v>571.35</v>
+        <v>115.5</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="O29" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P29" t="n">
-        <v>125.7</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="30">
@@ -2145,51 +2145,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>079106H</t>
+          <t>079105K</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79106</t>
+          <t>79105</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GIN  GREATER THAN LONDON</t>
+          <t>JAISALMIR INDIA CEAFT GIN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>454.15</v>
+        <v>1904.46</v>
       </c>
       <c r="G30" t="n">
-        <v>499.57</v>
+        <v>2094.91</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>3496.99</v>
+        <v>31423.65</v>
       </c>
       <c r="L30" t="n">
-        <v>3179.05</v>
+        <v>28566.9</v>
       </c>
       <c r="M30" t="n">
-        <v>317.94</v>
+        <v>2856.75</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>298</v>
       </c>
       <c r="O30" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>69.93000000000001</v>
+        <v>552.75</v>
       </c>
     </row>
     <row r="31">
@@ -2203,51 +2203,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>079152L</t>
+          <t>078154K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VODKA M/M GREEN APPLEV</t>
+          <t>RUM OLD MONK 7 YEARS OLD</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>281.32</v>
+        <v>117.88</v>
       </c>
       <c r="G31" t="n">
-        <v>309.45</v>
+        <v>129.67</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K31" t="n">
-        <v>11140.2</v>
+        <v>5964.82</v>
       </c>
       <c r="L31" t="n">
-        <v>10127.52</v>
+        <v>5422.48</v>
       </c>
       <c r="M31" t="n">
-        <v>1012.68</v>
+        <v>542.34</v>
       </c>
       <c r="N31" t="n">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="O31" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="32">
@@ -2261,51 +2261,51 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>079153V</t>
+          <t>078195A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>79153</t>
+          <t>78195</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VODKA ORANGE MAGIC MOMENT 750 ML</t>
+          <t>RUM MADIRA</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>281.32</v>
+        <v>112.69</v>
       </c>
       <c r="G32" t="n">
-        <v>309.45</v>
+        <v>123.96</v>
       </c>
       <c r="H32" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>11449.65</v>
+        <v>5082.36</v>
       </c>
       <c r="L32" t="n">
-        <v>10408.84</v>
+        <v>4620.29</v>
       </c>
       <c r="M32" t="n">
-        <v>1040.81</v>
+        <v>462.07</v>
       </c>
       <c r="N32" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2319,51 +2319,51 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>079156X</t>
+          <t>079312W</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>79156</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VODKA SMIRNOFF 750 ML</t>
+          <t>WHISKY WHITE&amp; BLUE PREMIUM</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>358.64</v>
+        <v>300.45</v>
       </c>
       <c r="G33" t="n">
-        <v>394.5</v>
+        <v>330.5</v>
       </c>
       <c r="H33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>8284.5</v>
+        <v>8262.5</v>
       </c>
       <c r="L33" t="n">
-        <v>7531.44</v>
+        <v>7511.25</v>
       </c>
       <c r="M33" t="n">
-        <v>753.0599999999999</v>
+        <v>751.25</v>
       </c>
       <c r="N33" t="n">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="O33" t="n">
-        <v>15</v>
+        <v>198</v>
       </c>
       <c r="P33" t="n">
-        <v>165.69</v>
+        <v>145.34</v>
       </c>
     </row>
     <row r="34">
@@ -2377,51 +2377,51 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>079162D</t>
+          <t>076010X</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>79162</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VODKA MAGIC MOVEMENT</t>
+          <t>WHISKY TEACHER HIGHLAND 750ML</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>289.99</v>
+        <v>719.84</v>
       </c>
       <c r="G34" t="n">
-        <v>318.99</v>
+        <v>791.8200000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>11802.63</v>
+        <v>9501.84</v>
       </c>
       <c r="L34" t="n">
-        <v>10729.63</v>
+        <v>8638.08</v>
       </c>
       <c r="M34" t="n">
-        <v>1073</v>
+        <v>863.76</v>
       </c>
       <c r="N34" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="O34" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>167.14</v>
       </c>
     </row>
     <row r="35">
@@ -2435,51 +2435,51 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>079198T</t>
+          <t>079243J</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>79198</t>
+          <t>79243</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WHISKY MC.DOWEL NO.1 750 ML.</t>
+          <t>WHY AFTER DARK GRAIN</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>265.3</v>
+        <v>368.4</v>
       </c>
       <c r="G35" t="n">
-        <v>291.83</v>
+        <v>405.24</v>
       </c>
       <c r="H35" t="n">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="K35" t="n">
-        <v>49027.44</v>
+        <v>12967.68</v>
       </c>
       <c r="L35" t="n">
-        <v>44570.4</v>
+        <v>11788.8</v>
       </c>
       <c r="M35" t="n">
-        <v>4457.04</v>
+        <v>1178.88</v>
       </c>
       <c r="N35" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="O35" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>228.11</v>
       </c>
     </row>
     <row r="36">
@@ -2493,51 +2493,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>079230S</t>
+          <t>078202A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>79230</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WHISKY BLENDER PRIDE R/PRIMIUM</t>
+          <t>XXX SUNNY RUM 750 ML</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>436.33</v>
+        <v>109.46</v>
       </c>
       <c r="G36" t="n">
-        <v>479.96</v>
+        <v>120.41</v>
       </c>
       <c r="H36" t="n">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>109430.88</v>
+        <v>4936.81</v>
       </c>
       <c r="L36" t="n">
-        <v>99483.24000000001</v>
+        <v>4487.86</v>
       </c>
       <c r="M36" t="n">
-        <v>9947.639999999999</v>
+        <v>448.95</v>
       </c>
       <c r="N36" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="O36" t="n">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="P36" t="n">
-        <v>2188.8</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="37">
@@ -2551,51 +2551,51 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>079232K</t>
+          <t>078208T</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>79232</t>
+          <t>78208</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WHISKY ROYAL STAG BLENDED</t>
+          <t>RUM COMMANDER IN CHIEF 750ML</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>293.95</v>
+        <v>130.14</v>
       </c>
       <c r="G37" t="n">
-        <v>323.35</v>
+        <v>143.15</v>
       </c>
       <c r="H37" t="n">
-        <v>299</v>
+        <v>33</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>299</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>96681.64999999999</v>
+        <v>4723.95</v>
       </c>
       <c r="L37" t="n">
-        <v>87891.05</v>
+        <v>4294.62</v>
       </c>
       <c r="M37" t="n">
-        <v>8790.6</v>
+        <v>429.33</v>
       </c>
       <c r="N37" t="n">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="O37" t="n">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="P37" t="n">
-        <v>1934.53</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2609,51 +2609,51 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>079243J</t>
+          <t>078152S</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>79243</t>
+          <t>78152</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WHY AFTER DARK GRAIN</t>
+          <t>RUM CONTESSA 5 YEAR OLD</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>368.4</v>
+        <v>112.33</v>
       </c>
       <c r="G38" t="n">
-        <v>405.24</v>
+        <v>123.56</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="K38" t="n">
-        <v>9725.76</v>
+        <v>8031.4</v>
       </c>
       <c r="L38" t="n">
-        <v>8841.6</v>
+        <v>7301.45</v>
       </c>
       <c r="M38" t="n">
-        <v>884.16</v>
+        <v>729.95</v>
       </c>
       <c r="N38" t="n">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="O38" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="P38" t="n">
-        <v>194.4</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="39">
@@ -2667,51 +2667,51 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>079266A</t>
+          <t>076003P</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>79266</t>
+          <t>76003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FRATELLI WINES SETTLE 750 ML</t>
+          <t>S/W BALLENTINES</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1195.58</v>
+        <v>992.25</v>
       </c>
       <c r="G39" t="n">
-        <v>1315.14</v>
+        <v>1091.48</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K39" t="n">
-        <v>3945.42</v>
+        <v>45842.16</v>
       </c>
       <c r="L39" t="n">
-        <v>3586.74</v>
+        <v>41674.5</v>
       </c>
       <c r="M39" t="n">
-        <v>358.68</v>
+        <v>4167.66</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="P39" t="n">
-        <v>78.90000000000001</v>
+        <v>806.38</v>
       </c>
     </row>
     <row r="40">
@@ -2725,51 +2725,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>079276K</t>
+          <t>076018A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79276</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>B BACARDI CRANE</t>
+          <t>SCOTCH WKY B/DOG TRIPLE</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42.37</v>
+        <v>1038.34</v>
       </c>
       <c r="G40" t="n">
-        <v>44.49</v>
+        <v>1142.17</v>
       </c>
       <c r="H40" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>1201.23</v>
+        <v>46828.97</v>
       </c>
       <c r="L40" t="n">
-        <v>1143.99</v>
+        <v>42571.94</v>
       </c>
       <c r="M40" t="n">
-        <v>57.24</v>
+        <v>4257.03</v>
       </c>
       <c r="N40" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="O40" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>823.74</v>
       </c>
     </row>
     <row r="41">
@@ -2783,51 +2783,51 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>079283G</t>
+          <t>078209P</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>79283</t>
+          <t>78209</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WINE CLASSIC SHIRAZ 750ML</t>
+          <t>BACARDI CLSSIC BLACK ORIGINAAL</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>317.47</v>
+        <v>146.32</v>
       </c>
       <c r="G41" t="n">
-        <v>349.22</v>
+        <v>160.95</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>2095.32</v>
+        <v>2253.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1904.82</v>
+        <v>2048.48</v>
       </c>
       <c r="M41" t="n">
-        <v>190.5</v>
+        <v>204.82</v>
       </c>
       <c r="N41" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="P41" t="n">
-        <v>41.88</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="42">
@@ -2841,51 +2841,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>079312W</t>
+          <t>076001D</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>79312</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WHISKY WHITE&amp; BLUE PREMIUM</t>
+          <t>WHISKY 100 PIPER 750 ML</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>300.45</v>
+        <v>742.62</v>
       </c>
       <c r="G42" t="n">
-        <v>330.5</v>
+        <v>816.88</v>
       </c>
       <c r="H42" t="n">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>37346.5</v>
+        <v>11436.32</v>
       </c>
       <c r="L42" t="n">
-        <v>33950.85</v>
+        <v>10396.68</v>
       </c>
       <c r="M42" t="n">
-        <v>3395.65</v>
+        <v>1039.64</v>
       </c>
       <c r="N42" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="O42" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P42" t="n">
-        <v>746.9299999999999</v>
+        <v>201.17</v>
       </c>
     </row>
     <row r="43">
@@ -2919,31 +2919,31 @@
         <v>1448.82</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>24629.94</v>
+        <v>21732.3</v>
       </c>
       <c r="L43" t="n">
-        <v>22390.87</v>
+        <v>19756.65</v>
       </c>
       <c r="M43" t="n">
-        <v>2239.07</v>
+        <v>1975.65</v>
       </c>
       <c r="N43" t="n">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="O43" t="n">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="P43" t="n">
-        <v>492.66</v>
+        <v>382.28</v>
       </c>
     </row>
     <row r="44">
@@ -2957,51 +2957,51 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>079317P</t>
+          <t>079324E</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>79317</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WHY ROCK FORD</t>
+          <t>WHY DENNIS 750ML</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>494.2</v>
+        <v>239.6</v>
       </c>
       <c r="G44" t="n">
-        <v>543.62</v>
+        <v>263.56</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="K44" t="n">
-        <v>13046.88</v>
+        <v>16867.84</v>
       </c>
       <c r="L44" t="n">
-        <v>11860.8</v>
+        <v>15334.4</v>
       </c>
       <c r="M44" t="n">
-        <v>1186.08</v>
+        <v>1533.44</v>
       </c>
       <c r="N44" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="O44" t="n">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="P44" t="n">
-        <v>260.88</v>
+        <v>296.71</v>
       </c>
     </row>
     <row r="45">
@@ -3015,51 +3015,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>079318A</t>
+          <t>079276K</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>79318</t>
+          <t>79276</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>STERLING RESRVE B10 WHY</t>
+          <t>B BACARDI CRANE</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>439.27</v>
+        <v>42.37</v>
       </c>
       <c r="G45" t="n">
-        <v>483.2</v>
+        <v>44.49</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>11596.8</v>
+        <v>1067.76</v>
       </c>
       <c r="L45" t="n">
-        <v>10542.48</v>
+        <v>1016.88</v>
       </c>
       <c r="M45" t="n">
-        <v>1054.32</v>
+        <v>50.88</v>
       </c>
       <c r="N45" t="n">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>231.84</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="46">
@@ -3073,51 +3073,51 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>079322A</t>
+          <t>078155X</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>79322</t>
+          <t>78155</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WHISKY BLEDERS PRAIDE R</t>
+          <t>RUM OLD SMUGLER XXX 750ML</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>508.76</v>
+        <v>120.4</v>
       </c>
       <c r="G46" t="n">
-        <v>559.64</v>
+        <v>132.44</v>
       </c>
       <c r="H46" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K46" t="n">
-        <v>26862.72</v>
+        <v>7019.32</v>
       </c>
       <c r="L46" t="n">
-        <v>24420.48</v>
+        <v>6381.2</v>
       </c>
       <c r="M46" t="n">
-        <v>2442.24</v>
+        <v>638.12</v>
       </c>
       <c r="N46" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="P46" t="n">
-        <v>537.12</v>
+        <v>123.47</v>
       </c>
     </row>
     <row r="47">
@@ -3131,51 +3131,51 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>079324E</t>
+          <t>079325W</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>79324</t>
+          <t>79325</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>WHY DENNIS 750ML</t>
+          <t>WHISKY OFFICER CHOICE BLUE 750ML</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>239.6</v>
+        <v>266.94</v>
       </c>
       <c r="G47" t="n">
-        <v>263.56</v>
+        <v>293.63</v>
       </c>
       <c r="H47" t="n">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="K47" t="n">
-        <v>46913.68</v>
+        <v>11451.57</v>
       </c>
       <c r="L47" t="n">
-        <v>42648.8</v>
+        <v>10410.66</v>
       </c>
       <c r="M47" t="n">
-        <v>4264.88</v>
+        <v>1040.91</v>
       </c>
       <c r="N47" t="n">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="O47" t="n">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="P47" t="n">
-        <v>938.0599999999999</v>
+        <v>201.44</v>
       </c>
     </row>
     <row r="48">
@@ -3189,92 +3189,226 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>079329F</t>
+          <t>079106H</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>79329</t>
+          <t>79106</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OAKEN GLOW WHISKY</t>
+          <t>GIN  GREATER THAN LONDON</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>415.19</v>
+        <v>454.15</v>
       </c>
       <c r="G48" t="n">
-        <v>456.71</v>
+        <v>499.57</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K48" t="n">
-        <v>5480.52</v>
+        <v>20981.94</v>
       </c>
       <c r="L48" t="n">
-        <v>4982.28</v>
+        <v>19074.3</v>
       </c>
       <c r="M48" t="n">
-        <v>498.24</v>
+        <v>1907.64</v>
       </c>
       <c r="N48" t="n">
-        <v>12</v>
+        <v>233</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P48" t="n">
-        <v>109.56</v>
+        <v>369.08</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Group Total</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>079318A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>79318</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>STERLING RESRVE B10 WHY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>439.27</v>
+      </c>
+      <c r="G49" t="n">
+        <v>483.2</v>
+      </c>
       <c r="H49" t="n">
-        <v>4047</v>
+        <v>19</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4047</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>1225963.25</v>
+        <v>9180.799999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>1115807.94</v>
+        <v>8346.129999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>110155.31</v>
+        <v>834.67</v>
       </c>
       <c r="N49" t="n">
-        <v>21631.3</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="O49" t="n">
+        <v>80</v>
+      </c>
+      <c r="P49" t="n">
+        <v>161.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>079266A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>79266</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FRATELLI WINES SETTLE 750 ML</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1195.58</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1315.14</v>
+      </c>
+      <c r="H50" t="n">
+        <v>20</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" t="n">
+        <v>22357.38</v>
+      </c>
+      <c r="L50" t="n">
+        <v>20324.86</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2032.52</v>
+      </c>
+      <c r="N50" t="n">
+        <v>299</v>
+      </c>
+      <c r="O50" t="n">
+        <v>176</v>
+      </c>
+      <c r="P50" t="n">
+        <v>393.27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>079311F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>79311</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>WHISKY RED NIGHT</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>291.11</v>
+      </c>
+      <c r="G51" t="n">
+        <v>320.22</v>
+      </c>
+      <c r="H51" t="n">
+        <v>37</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>36</v>
+      </c>
+      <c r="K51" t="n">
+        <v>11527.92</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10479.96</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1047.96</v>
+      </c>
+      <c r="N51" t="n">
+        <v>250</v>
+      </c>
+      <c r="O51" t="n">
+        <v>136</v>
+      </c>
+      <c r="P51" t="n">
+        <v>202.78</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
